--- a/Results/Two_Datasets_Assessment/Cancer/Tables/fidelity_scores.xlsx
+++ b/Results/Two_Datasets_Assessment/Cancer/Tables/fidelity_scores.xlsx
@@ -478,13 +478,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5133862651733053</v>
+        <v>0.5275669612932169</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4190367853106954</v>
+        <v>0.3925352606417877</v>
       </c>
       <c r="G2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -505,10 +505,10 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4750360720991947</v>
+        <v>0.4872794696822143</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3313262612729288</v>
+        <v>0.2798978131734407</v>
       </c>
       <c r="G3" t="n">
         <v>9</v>
@@ -532,13 +532,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3682877872336551</v>
+        <v>0.493020634446126</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2472718850136229</v>
+        <v>0.2113072186826778</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -559,13 +559,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2648177399141864</v>
+        <v>0.4849657455036203</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3973204760397929</v>
+        <v>0.4728531538294638</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -586,13 +586,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3928241452145236</v>
+        <v>0.519908292713704</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4460124703686378</v>
+        <v>0.4595556126630457</v>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -613,13 +613,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.413774075177361</v>
+        <v>0.5372078162303315</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4362112587722336</v>
+        <v>0.4465408135061384</v>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -640,13 +640,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5143939653183046</v>
+        <v>0.4629545687864741</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4731592883193763</v>
+        <v>0.4746639280065832</v>
       </c>
       <c r="G8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -667,13 +667,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.255724578002569</v>
+        <v>0.4785157516103453</v>
       </c>
       <c r="F9" t="n">
-        <v>0.407271732796022</v>
+        <v>0.4815889446704471</v>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
